--- a/20250812_Finance/01_source/CompanyABC43_COA.xlsx
+++ b/20250812_Finance/01_source/CompanyABC43_COA.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renjinhu/Desktop/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/i0515899/Documents/Git/AI_Power_Studio/20250812_Finance/01_source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF13D816-80F4-CA48-BBF9-180F31F1B005}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAEA94D-6104-1546-9833-2195593A4C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="13900" xr2:uid="{9A7285AE-49E6-4CC9-B5A1-C349D09A87EB}"/>
+    <workbookView xWindow="2400" yWindow="-20240" windowWidth="26980" windowHeight="19700" xr2:uid="{9A7285AE-49E6-4CC9-B5A1-C349D09A87EB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="balance_sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="income" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">balance_sheet!$A$1:$F$2205</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5820,8 +5821,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0;[Red]\-#,##0;&quot;－&quot;"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="#,##0;[Red]\-#,##0;&quot;－&quot;"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -5846,7 +5847,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5921,7 +5922,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5972,10 +5973,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -6026,7 +6027,7 @@
     <xf numFmtId="38" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6047,76 +6048,10 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 4 2" xfId="2" xr:uid="{1D3F0BDB-9DB4-449B-9950-C3DE78BED77E}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="標準 3" xfId="1" xr:uid="{D2CDEB87-7C14-482D-8148-83C8838B10B4}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -46217,21 +46152,29 @@
       <c r="F2205" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2205" xr:uid="{58F9EE6B-4CCB-40AB-AE40-DBC467F9F8D9}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2194:A1048576 A1847:A1848 A2055 A2124:A2133 A2008:A2047 A2154:A2155 A2:A389">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2196:A2199 A2124:A2132 A2201 A2203:A2205 A2:A389">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7D9E91-8C95-D64A-B58E-B5D17B3E0C58}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
